--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486717_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486717_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.276899999999999</v>
+        <v>8.385899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5184</v>
+        <v>8.677</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2415</v>
+        <v>-0.2912</v>
       </c>
       <c r="G2" t="n">
         <v>7.9896</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8052</v>
+        <v>-0.6962</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8829</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0281</v>
       </c>
       <c r="V2" t="n">
         <v>0.8995</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6068</v>
+        <v>4.3517</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4908</v>
+        <v>4.2357</v>
       </c>
       <c r="F3" t="n">
         <v>0.116</v>
@@ -688,10 +688,10 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5792</v>
+        <v>-0.8343</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.359</v>
+        <v>-0.6141</v>
       </c>
       <c r="U3" t="n">
         <v>-0.2203</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4048</v>
+        <v>3.1497</v>
       </c>
       <c r="E4" t="n">
-        <v>3.082</v>
+        <v>2.8269</v>
       </c>
       <c r="F4" t="n">
         <v>0.3228</v>
@@ -766,10 +766,10 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001</v>
+        <v>-0.255</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1934</v>
+        <v>-0.4485</v>
       </c>
       <c r="U4" t="n">
         <v>0.1936</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3639</v>
+        <v>2.5538</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9252</v>
+        <v>1.9616</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5613</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.424</v>
+        <v>2.5606</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6824</v>
+        <v>0.3995</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.2584</v>
+        <v>2.1612</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7843</v>
+        <v>2.7411</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3041</v>
+        <v>0.7449</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5198</v>
+        <v>1.9962</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3602</v>
+        <v>-0.1805</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6217</v>
+        <v>-0.3454</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7385</v>
+        <v>0.165</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-1.3584</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8277</v>
+        <v>-0.7795</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0612</v>
+        <v>-0.5789</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1271</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1271</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2517</v>
+        <v>2.5514</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8582</v>
+        <v>3.1872</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3935</v>
+        <v>-0.6358</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5606</v>
+        <v>0.424</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3995</v>
+        <v>2.6824</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1612</v>
+        <v>-2.2584</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7411</v>
+        <v>2.7843</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7449</v>
+        <v>3.3041</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9962</v>
+        <v>-0.5198</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1805</v>
+        <v>-2.3602</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3454</v>
+        <v>-0.6217</v>
       </c>
       <c r="O6" t="n">
-        <v>0.165</v>
+        <v>-1.7385</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6604</v>
+        <v>-0.579</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8829</v>
+        <v>-0.5657</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7775</v>
+        <v>-0.0133</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0731</v>
+        <v>1.2069</v>
       </c>
       <c r="E7" t="n">
-        <v>1.055</v>
+        <v>1.2136</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0181</v>
+        <v>-0.0068</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7671</v>
@@ -1000,13 +1000,13 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2024</v>
+        <v>-1.0687</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8829</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3195</v>
+        <v>-0.3444</v>
       </c>
       <c r="V7" t="n">
         <v>1.8842</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1462</v>
+        <v>-1.3945</v>
       </c>
       <c r="E8" t="n">
         <v>-2.9043</v>
       </c>
       <c r="F8" t="n">
-        <v>1.758</v>
+        <v>1.5097</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0636</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4688</v>
+        <v>-0.7171</v>
       </c>
       <c r="T8" t="n">
         <v>-0.7174</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2486</v>
+        <v>0.0003</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9159</v>
+        <v>-2.6676</v>
       </c>
       <c r="E9" t="n">
         <v>-2.6641</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2519</v>
+        <v>-0.0035</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1301</v>
@@ -1156,13 +1156,13 @@
         <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.855</v>
+        <v>-0.6067</v>
       </c>
       <c r="T9" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4688</v>
+        <v>-0.2204</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2344</v>
+        <v>-4.1806</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5042</v>
+        <v>-4.4007</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2698</v>
+        <v>0.2201</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3327</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9708</v>
+        <v>-0.9171</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3087</v>
+        <v>-0.3583</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.6807</v>
+        <v>13.9567</v>
       </c>
       <c r="E11" t="n">
-        <v>11.857</v>
+        <v>12.1329</v>
       </c>
       <c r="F11" t="n">
         <v>1.8235</v>
@@ -1279,7 +1279,7 @@
         <v>11.997</v>
       </c>
       <c r="H11" t="n">
-        <v>5.859500000000001</v>
+        <v>5.8595</v>
       </c>
       <c r="I11" t="n">
         <v>6.137700000000001</v>
@@ -1300,7 +1300,7 @@
         <v>-2.0754</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.2459</v>
+        <v>-7.245899999999999</v>
       </c>
       <c r="P11" t="n">
         <v>2.8961</v>
@@ -1312,19 +1312,19 @@
         <v>13.5153</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.3083</v>
+        <v>-7.032499999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.794700000000001</v>
+        <v>-5.518899999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5137</v>
+        <v>-1.5136</v>
       </c>
       <c r="V11" t="n">
         <v>6.0959</v>
       </c>
       <c r="W11" t="n">
-        <v>6.952599999999999</v>
+        <v>6.9526</v>
       </c>
       <c r="X11" t="n">
         <v>-0.8568</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2247</v>
+        <v>3.4634</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4461</v>
+        <v>1.0324</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7786</v>
+        <v>2.431</v>
       </c>
       <c r="G12" t="n">
         <v>2.5077</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1957</v>
+        <v>1.4343</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8547</v>
+        <v>0.441</v>
       </c>
       <c r="U12" t="n">
-        <v>1.341</v>
+        <v>0.9933</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5891</v>
+        <v>1.6554</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6179</v>
+        <v>1.411</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0287</v>
+        <v>0.2444</v>
       </c>
       <c r="G13" t="n">
         <v>0.1138</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.0204</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6339</v>
+        <v>0.4271</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3201</v>
+        <v>0.5933</v>
       </c>
       <c r="V13" t="n">
         <v>0.3282</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7267</v>
+        <v>1.5997</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5873</v>
+        <v>5.3113</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.8606</v>
+        <v>-3.7116</v>
       </c>
       <c r="G14" t="n">
         <v>6.0011</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2318</v>
+        <v>0.6412</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8002</v>
+        <v>-0.0762</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5684</v>
+        <v>0.7174</v>
       </c>
       <c r="V14" t="n">
         <v>-3.1118</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3097</v>
+        <v>-0.994</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2275</v>
+        <v>-1.8417</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5371</v>
+        <v>0.8477</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.2277</v>
+        <v>0.1231</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.227</v>
+        <v>0.0757</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0007</v>
+        <v>0.0475</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1513</v>
+        <v>0.3099</v>
       </c>
       <c r="K15" t="n">
-        <v>0.187</v>
+        <v>0.1448</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3383</v>
+        <v>0.1651</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0764</v>
+        <v>-0.1868</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.414</v>
+        <v>-0.0692</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6624</v>
+        <v>-0.1176</v>
       </c>
       <c r="P15" t="n">
+        <v>-1.7377</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.3169</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.5792</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.1931</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.7723</v>
-      </c>
       <c r="S15" t="n">
-        <v>1.9526</v>
+        <v>0.6206</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5718</v>
+        <v>0.1653</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3808</v>
+        <v>0.4553</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6809</v>
+        <v>-1.3936</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2554</v>
+        <v>-0.8068</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5746</v>
+        <v>-0.5868</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1231</v>
+        <v>-2.2277</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0757</v>
+        <v>-0.227</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0475</v>
+        <v>-2.0007</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3099</v>
+        <v>-1.1513</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1448</v>
+        <v>0.187</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1651</v>
+        <v>-1.3383</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1868</v>
+        <v>-1.0764</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0692</v>
+        <v>-0.414</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1176</v>
+        <v>-0.6624</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7377</v>
+        <v>0.5792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3169</v>
+        <v>-0.1931</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0663</v>
+        <v>0.8687</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2484</v>
+        <v>0.5376</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1821</v>
+        <v>0.3312</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6388</v>
+        <v>-2.8333</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2464</v>
+        <v>-1.143</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3924</v>
+        <v>-1.6904</v>
       </c>
       <c r="G17" t="n">
         <v>-2.192</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1377</v>
+        <v>0.2411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7671</v>
+        <v>0.4691</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.0258</v>
+        <v>-3.5337</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9105</v>
+        <v>-3.2226</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.9363</v>
+        <v>-0.3112</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.996</v>
+        <v>-5.2302</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0145</v>
+        <v>-0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0105</v>
+        <v>-4.6162</v>
       </c>
       <c r="J18" t="n">
-        <v>1.046</v>
+        <v>-3.1398</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8425</v>
+        <v>0.1448</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2035</v>
+        <v>-3.2846</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.042</v>
+        <v>-2.0904</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.828</v>
+        <v>-0.7588</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.214</v>
+        <v>-1.3316</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2245</v>
+        <v>0.2757</v>
       </c>
       <c r="T18" t="n">
-        <v>0.772</v>
+        <v>-0.152</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4526</v>
+        <v>0.4277</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.6404</v>
+        <v>1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.9261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3946</v>
+        <v>-3.5395</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4213</v>
+        <v>-1.3179</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9733</v>
+        <v>-2.2216</v>
       </c>
       <c r="G19" t="n">
         <v>-4.8841</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9102</v>
+        <v>0.7653</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2211</v>
+        <v>-0.1177</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1313</v>
+        <v>0.883</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3281</v>
+        <v>-3.6712</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8431</v>
+        <v>1.2899</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.485</v>
+        <v>-4.9611</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.2302</v>
+        <v>-0.996</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.614</v>
+        <v>0.0145</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.6162</v>
+        <v>-1.0105</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1398</v>
+        <v>1.046</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1448</v>
+        <v>0.8425</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.2846</v>
+        <v>0.2035</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0904</v>
+        <v>-2.042</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7588</v>
+        <v>-0.828</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3316</v>
+        <v>-1.214</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5187</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7725</v>
+        <v>0.1514</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2539</v>
+        <v>0.4277</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2277</v>
+        <v>-3.6404</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.9261</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8434</v>
+        <v>-4.4338</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8464</v>
+        <v>-2.5362</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.997</v>
+        <v>-1.8976</v>
       </c>
       <c r="G21" t="n">
         <v>-5.2128</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0167</v>
+        <v>0.3929</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4142</v>
+        <v>-0.1039</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3974</v>
+        <v>0.4968</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.6808</v>
+        <v>-13.6806</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8233</v>
+        <v>-1.823599999999999</v>
       </c>
       <c r="F22" t="n">
         <v>-11.8572</v>
@@ -2137,19 +2137,19 @@
         <v>-11.9971</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.8594</v>
+        <v>-5.859400000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.137700000000001</v>
+        <v>-6.1377</v>
       </c>
       <c r="J22" t="n">
-        <v>9.321400000000002</v>
+        <v>9.321399999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0752</v>
+        <v>2.075200000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>7.246099999999999</v>
+        <v>7.2461</v>
       </c>
       <c r="M22" t="n">
         <v>-21.3185</v>
@@ -2170,16 +2170,16 @@
         <v>10.6191</v>
       </c>
       <c r="S22" t="n">
-        <v>7.3083</v>
+        <v>7.3084</v>
       </c>
       <c r="T22" t="n">
         <v>1.5137</v>
       </c>
       <c r="U22" t="n">
-        <v>5.7947</v>
+        <v>5.7948</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.095699999999999</v>
+        <v>-6.095700000000001</v>
       </c>
       <c r="W22" t="n">
         <v>0.8568</v>
